--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/194.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/194.xlsx
@@ -426,13 +426,13 @@
         <v>3.564489754266518</v>
       </c>
       <c r="E2">
-        <v>-14.65627687678649</v>
+        <v>-14.64873243908971</v>
       </c>
       <c r="F2">
-        <v>-1.418639795362066</v>
+        <v>-1.576603660504112</v>
       </c>
       <c r="G2">
-        <v>-10.55687070957419</v>
+        <v>-10.96285615123717</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.491780965806519</v>
       </c>
       <c r="E3">
-        <v>-15.07240741029934</v>
+        <v>-15.25305729541332</v>
       </c>
       <c r="F3">
-        <v>-1.470541154984468</v>
+        <v>-1.668243461173613</v>
       </c>
       <c r="G3">
-        <v>-9.606131688878595</v>
+        <v>-11.12016334362672</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.454384077838746</v>
       </c>
       <c r="E4">
-        <v>-15.27279238513875</v>
+        <v>-14.99700831807163</v>
       </c>
       <c r="F4">
-        <v>-1.066661515708139</v>
+        <v>-1.376804756418482</v>
       </c>
       <c r="G4">
-        <v>-9.475196302254879</v>
+        <v>-10.37851506864595</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.46668162920223</v>
       </c>
       <c r="E5">
-        <v>-15.21807030523006</v>
+        <v>-16.02998946701329</v>
       </c>
       <c r="F5">
-        <v>-1.304230659891815</v>
+        <v>-0.9704168206464754</v>
       </c>
       <c r="G5">
-        <v>-9.099449383547601</v>
+        <v>-10.43105673689973</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.529659635781824</v>
       </c>
       <c r="E6">
-        <v>-15.26494906815746</v>
+        <v>-17.15405181367124</v>
       </c>
       <c r="F6">
-        <v>-1.567479193562275</v>
+        <v>-1.44807417428574</v>
       </c>
       <c r="G6">
-        <v>-8.302286570418795</v>
+        <v>-9.983729202542326</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.651780580362308</v>
       </c>
       <c r="E7">
-        <v>-16.26194696263418</v>
+        <v>-17.03432801785645</v>
       </c>
       <c r="F7">
-        <v>-1.010233128229436</v>
+        <v>-1.249525276610935</v>
       </c>
       <c r="G7">
-        <v>-9.351610326728347</v>
+        <v>-10.22918960155159</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.837111778031715</v>
       </c>
       <c r="E8">
-        <v>-17.20829387533511</v>
+        <v>-18.26375889772487</v>
       </c>
       <c r="F8">
-        <v>-1.482180545361204</v>
+        <v>-1.125796179491787</v>
       </c>
       <c r="G8">
-        <v>-8.361505609025278</v>
+        <v>-9.198534011537987</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.08049929577399</v>
       </c>
       <c r="E9">
-        <v>-18.1337781082827</v>
+        <v>-17.8858713272068</v>
       </c>
       <c r="F9">
-        <v>-1.046047592889473</v>
+        <v>-0.9909984371364319</v>
       </c>
       <c r="G9">
-        <v>-6.94668107245249</v>
+        <v>-9.015344974122415</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.380331753925646</v>
       </c>
       <c r="E10">
-        <v>-19.4583069423122</v>
+        <v>-18.67875278426179</v>
       </c>
       <c r="F10">
-        <v>-1.01210441019236</v>
+        <v>-1.10087640291337</v>
       </c>
       <c r="G10">
-        <v>-7.862103193335141</v>
+        <v>-8.908103161923265</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.730145831910143</v>
       </c>
       <c r="E11">
-        <v>-18.53614660928624</v>
+        <v>-19.51706842103573</v>
       </c>
       <c r="F11">
-        <v>-0.9022653776833545</v>
+        <v>-0.5076303186222672</v>
       </c>
       <c r="G11">
-        <v>-7.132713868486295</v>
+        <v>-8.635307588396241</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.107444860758656</v>
       </c>
       <c r="E12">
-        <v>-18.04301390374697</v>
+        <v>-19.61919909533072</v>
       </c>
       <c r="F12">
-        <v>-1.232422803212737</v>
+        <v>-0.8303721991617882</v>
       </c>
       <c r="G12">
-        <v>-7.804794339504817</v>
+        <v>-8.343549210020271</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.493006544905703</v>
       </c>
       <c r="E13">
-        <v>-19.14951482820317</v>
+        <v>-21.77189072740896</v>
       </c>
       <c r="F13">
-        <v>-1.188246797988842</v>
+        <v>-0.5987300237451428</v>
       </c>
       <c r="G13">
-        <v>-6.629514257062614</v>
+        <v>-7.854366448409864</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.867886626813555</v>
       </c>
       <c r="E14">
-        <v>-20.89830280658927</v>
+        <v>-21.51822825586931</v>
       </c>
       <c r="F14">
-        <v>-0.5177264605275875</v>
+        <v>-0.415776799162844</v>
       </c>
       <c r="G14">
-        <v>-5.930214480620204</v>
+        <v>-6.377578430978537</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.205515387371783</v>
       </c>
       <c r="E15">
-        <v>-20.89338035534294</v>
+        <v>-21.960248075284</v>
       </c>
       <c r="F15">
-        <v>0.1753610900881336</v>
+        <v>-0.2753826066341754</v>
       </c>
       <c r="G15">
-        <v>-6.648308224089057</v>
+        <v>-6.384156484965069</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.488979131819255</v>
       </c>
       <c r="E16">
-        <v>-21.65830754234857</v>
+        <v>-23.01564064208963</v>
       </c>
       <c r="F16">
-        <v>-0.1630642704885904</v>
+        <v>0.07847275355449501</v>
       </c>
       <c r="G16">
-        <v>-4.814600360432285</v>
+        <v>-6.514439694117548</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.709173102034272</v>
       </c>
       <c r="E17">
-        <v>-22.94232011943144</v>
+        <v>-23.41521960310444</v>
       </c>
       <c r="F17">
-        <v>0.8613967490038226</v>
+        <v>0.4085630813242504</v>
       </c>
       <c r="G17">
-        <v>-4.489316087380116</v>
+        <v>-6.069780459464798</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.854781324195645</v>
       </c>
       <c r="E18">
-        <v>-24.43332471493092</v>
+        <v>-24.13435938941853</v>
       </c>
       <c r="F18">
-        <v>0.6973725479428953</v>
+        <v>0.2608718003443209</v>
       </c>
       <c r="G18">
-        <v>-6.085929300605364</v>
+        <v>-6.436310819390747</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.920383621809231</v>
       </c>
       <c r="E19">
-        <v>-25.63548059585113</v>
+        <v>-25.31554390720922</v>
       </c>
       <c r="F19">
-        <v>0.9146011305508291</v>
+        <v>0.4825536861097051</v>
       </c>
       <c r="G19">
-        <v>-5.378704078141938</v>
+        <v>-6.11324792239543</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.908994020398251</v>
       </c>
       <c r="E20">
-        <v>-26.04025371655274</v>
+        <v>-25.74183633639528</v>
       </c>
       <c r="F20">
-        <v>0.4678460228729998</v>
+        <v>0.8204389511398038</v>
       </c>
       <c r="G20">
-        <v>-3.962575186626677</v>
+        <v>-6.247831530203421</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.822256207904651</v>
       </c>
       <c r="E21">
-        <v>-26.14919521575527</v>
+        <v>-25.84096463242318</v>
       </c>
       <c r="F21">
-        <v>0.7571897864664503</v>
+        <v>0.8333316613969753</v>
       </c>
       <c r="G21">
-        <v>-5.697542719029147</v>
+        <v>-5.633430694115621</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.663390295367916</v>
       </c>
       <c r="E22">
-        <v>-24.53689544396034</v>
+        <v>-26.93402051755061</v>
       </c>
       <c r="F22">
-        <v>0.8073292086230989</v>
+        <v>1.013743454787485</v>
       </c>
       <c r="G22">
-        <v>-3.345741099567513</v>
+        <v>-5.520574196681866</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.443553189467856</v>
       </c>
       <c r="E23">
-        <v>-26.91410428886488</v>
+        <v>-27.03205292286866</v>
       </c>
       <c r="F23">
-        <v>1.210283561510501</v>
+        <v>1.106419543077888</v>
       </c>
       <c r="G23">
-        <v>-3.967968065310151</v>
+        <v>-5.672289877655586</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.173360138037472</v>
       </c>
       <c r="E24">
-        <v>-26.2550709380546</v>
+        <v>-27.48958276575963</v>
       </c>
       <c r="F24">
-        <v>0.4690355584634199</v>
+        <v>0.9390893277123882</v>
       </c>
       <c r="G24">
-        <v>-4.20694310560798</v>
+        <v>-4.447682666678242</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.860037579327702</v>
       </c>
       <c r="E25">
-        <v>-27.08731389118426</v>
+        <v>-27.59746007357035</v>
       </c>
       <c r="F25">
-        <v>1.059202601118316</v>
+        <v>1.310945111563892</v>
       </c>
       <c r="G25">
-        <v>-4.45686612000418</v>
+        <v>-4.969914604407193</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.515830552828183</v>
       </c>
       <c r="E26">
-        <v>-27.89907455637723</v>
+        <v>-27.250696704907</v>
       </c>
       <c r="F26">
-        <v>0.7579419440681923</v>
+        <v>1.155955913765299</v>
       </c>
       <c r="G26">
-        <v>-4.036188477237912</v>
+        <v>-5.586530195460766</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.153459503451064</v>
       </c>
       <c r="E27">
-        <v>-27.61354068477159</v>
+        <v>-27.93470006139557</v>
       </c>
       <c r="F27">
-        <v>0.9374160255587332</v>
+        <v>0.9224242323028677</v>
       </c>
       <c r="G27">
-        <v>-3.868039248207249</v>
+        <v>-5.23456623590761</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.779366363497267</v>
       </c>
       <c r="E28">
-        <v>-26.59226111266574</v>
+        <v>-27.85261241305853</v>
       </c>
       <c r="F28">
-        <v>1.336157301835498</v>
+        <v>1.019735864579337</v>
       </c>
       <c r="G28">
-        <v>-4.219258335014069</v>
+        <v>-5.808171219314971</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.40151061267253</v>
       </c>
       <c r="E29">
-        <v>-26.08805628817771</v>
+        <v>-27.26106238191056</v>
       </c>
       <c r="F29">
-        <v>0.7871849701218204</v>
+        <v>1.092474806219161</v>
       </c>
       <c r="G29">
-        <v>-4.409790162435744</v>
+        <v>-5.830557128251524</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.030401097707378</v>
       </c>
       <c r="E30">
-        <v>-27.54401049485782</v>
+        <v>-26.92211515938444</v>
       </c>
       <c r="F30">
-        <v>1.013885933980767</v>
+        <v>1.172611068765986</v>
       </c>
       <c r="G30">
-        <v>-3.630871765773862</v>
+        <v>-5.176472782784479</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.668156226011158</v>
       </c>
       <c r="E31">
-        <v>-26.31244217525778</v>
+        <v>-27.47956578125466</v>
       </c>
       <c r="F31">
-        <v>0.6252780761424487</v>
+        <v>0.9695599942569652</v>
       </c>
       <c r="G31">
-        <v>-4.681963353401385</v>
+        <v>-5.801950704246681</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.314518552092401</v>
       </c>
       <c r="E32">
-        <v>-26.76059807695287</v>
+        <v>-26.74088110112347</v>
       </c>
       <c r="F32">
-        <v>0.6843357017576366</v>
+        <v>1.152579488231488</v>
       </c>
       <c r="G32">
-        <v>-4.584590277454802</v>
+        <v>-6.009972143752325</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.97551506959088</v>
       </c>
       <c r="E33">
-        <v>-26.59919873484549</v>
+        <v>-26.58620654291748</v>
       </c>
       <c r="F33">
-        <v>0.659329774969328</v>
+        <v>0.8808335617431101</v>
       </c>
       <c r="G33">
-        <v>-4.937365320665078</v>
+        <v>-5.954566853607083</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.649421789849875</v>
       </c>
       <c r="E34">
-        <v>-25.89840379673647</v>
+        <v>-26.78685416924934</v>
       </c>
       <c r="F34">
-        <v>0.5389713048121709</v>
+        <v>0.844897327074862</v>
       </c>
       <c r="G34">
-        <v>-4.800696069167346</v>
+        <v>-5.970119796550579</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.332320152532155</v>
       </c>
       <c r="E35">
-        <v>-25.67091590496116</v>
+        <v>-26.30724348709697</v>
       </c>
       <c r="F35">
-        <v>0.8637708499802459</v>
+        <v>1.15922299480194</v>
       </c>
       <c r="G35">
-        <v>-4.823787124303763</v>
+        <v>-6.765418772540775</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.028345037219684</v>
       </c>
       <c r="E36">
-        <v>-23.2831828864628</v>
+        <v>-25.28617222479548</v>
       </c>
       <c r="F36">
-        <v>0.925174412080162</v>
+        <v>0.7738813896328604</v>
       </c>
       <c r="G36">
-        <v>-5.026081320026468</v>
+        <v>-6.392429538267708</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.736840390522304</v>
       </c>
       <c r="E37">
-        <v>-25.08169350945313</v>
+        <v>-25.0646166339702</v>
       </c>
       <c r="F37">
-        <v>0.583485283936408</v>
+        <v>0.8734875996150842</v>
       </c>
       <c r="G37">
-        <v>-5.870932541648475</v>
+        <v>-5.452079009474345</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.455488189813954</v>
       </c>
       <c r="E38">
-        <v>-22.6270885152835</v>
+        <v>-24.42766412242133</v>
       </c>
       <c r="F38">
-        <v>1.366964285545611</v>
+        <v>0.9029327473149954</v>
       </c>
       <c r="G38">
-        <v>-4.893133121714876</v>
+        <v>-6.02816690203616</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.188303347066861</v>
       </c>
       <c r="E39">
-        <v>-22.84690517208983</v>
+        <v>-24.20498547004215</v>
       </c>
       <c r="F39">
-        <v>0.9529164363999175</v>
+        <v>1.281108974449859</v>
       </c>
       <c r="G39">
-        <v>-5.42580320952915</v>
+        <v>-5.363005471194715</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.937232321183989</v>
       </c>
       <c r="E40">
-        <v>-23.0004476117939</v>
+        <v>-23.71147690116025</v>
       </c>
       <c r="F40">
-        <v>1.134577407833849</v>
+        <v>1.070804714961926</v>
       </c>
       <c r="G40">
-        <v>-5.624091645149337</v>
+        <v>-6.568990863513658</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.7025133582987824</v>
       </c>
       <c r="E41">
-        <v>-22.57982030359144</v>
+        <v>-23.74326226022009</v>
       </c>
       <c r="F41">
-        <v>1.357635211855283</v>
+        <v>1.07756419296877</v>
       </c>
       <c r="G41">
-        <v>-5.171367921562923</v>
+        <v>-6.21004496341818</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.4884695525097182</v>
       </c>
       <c r="E42">
-        <v>-23.59679782539</v>
+        <v>-23.00584555281104</v>
       </c>
       <c r="F42">
-        <v>0.9913112655196746</v>
+        <v>0.8582224451162949</v>
       </c>
       <c r="G42">
-        <v>-4.766726561388885</v>
+        <v>-6.814335393429046</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2987909861498781</v>
       </c>
       <c r="E43">
-        <v>-22.43531669800668</v>
+        <v>-23.38749628522948</v>
       </c>
       <c r="F43">
-        <v>1.530636430460349</v>
+        <v>1.026825032812495</v>
       </c>
       <c r="G43">
-        <v>-5.265612531974895</v>
+        <v>-6.340520184211935</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.1348680174510867</v>
       </c>
       <c r="E44">
-        <v>-20.83169801088446</v>
+        <v>-21.32139360465191</v>
       </c>
       <c r="F44">
-        <v>0.9743529280495631</v>
+        <v>0.7973407544801424</v>
       </c>
       <c r="G44">
-        <v>-7.290179967061729</v>
+        <v>-7.309149393001753</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.0004912668881677665</v>
       </c>
       <c r="E45">
-        <v>-21.57145141088146</v>
+        <v>-20.81669517649705</v>
       </c>
       <c r="F45">
-        <v>1.024921444520862</v>
+        <v>1.007159590670035</v>
       </c>
       <c r="G45">
-        <v>-6.346277222904728</v>
+        <v>-5.797378840856948</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1050423544106716</v>
       </c>
       <c r="E46">
-        <v>-21.40139815494542</v>
+        <v>-20.90545326704738</v>
       </c>
       <c r="F46">
-        <v>1.09829160212162</v>
+        <v>0.9223761869935053</v>
       </c>
       <c r="G46">
-        <v>-6.271250329348225</v>
+        <v>-6.379730285579064</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1795296561563169</v>
       </c>
       <c r="E47">
-        <v>-19.76275172137387</v>
+        <v>-20.63926503640251</v>
       </c>
       <c r="F47">
-        <v>1.203346812879458</v>
+        <v>1.017090059094795</v>
       </c>
       <c r="G47">
-        <v>-6.423465902698375</v>
+        <v>-7.059703097163208</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2248675571743372</v>
       </c>
       <c r="E48">
-        <v>-18.53472466844783</v>
+        <v>-20.40453158621492</v>
       </c>
       <c r="F48">
-        <v>1.07239186690569</v>
+        <v>0.8477386272664643</v>
       </c>
       <c r="G48">
-        <v>-5.845411546086233</v>
+        <v>-6.848410838664764</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2420289312106052</v>
       </c>
       <c r="E49">
-        <v>-18.46926104819295</v>
+        <v>-20.07519378553309</v>
       </c>
       <c r="F49">
-        <v>1.310169759674872</v>
+        <v>0.9023230689065349</v>
       </c>
       <c r="G49">
-        <v>-6.999868297086421</v>
+        <v>-6.895831092969285</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.2344448763990754</v>
       </c>
       <c r="E50">
-        <v>-18.5671802416608</v>
+        <v>-18.98543010100924</v>
       </c>
       <c r="F50">
-        <v>0.6943374097790379</v>
+        <v>0.9289037221275654</v>
       </c>
       <c r="G50">
-        <v>-6.718534826613616</v>
+        <v>-6.939219102806972</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2050415496991737</v>
       </c>
       <c r="E51">
-        <v>-17.9372378078758</v>
+        <v>-18.33765000810802</v>
       </c>
       <c r="F51">
-        <v>1.225164353534392</v>
+        <v>0.6977428281719467</v>
       </c>
       <c r="G51">
-        <v>-6.274034498146753</v>
+        <v>-6.923338415855089</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1561047630660164</v>
       </c>
       <c r="E52">
-        <v>-17.230660008459</v>
+        <v>-18.69236537712884</v>
       </c>
       <c r="F52">
-        <v>0.7896982368219141</v>
+        <v>0.9666259169162493</v>
       </c>
       <c r="G52">
-        <v>-7.267661636303607</v>
+        <v>-7.158930078611784</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.09171032316524125</v>
       </c>
       <c r="E53">
-        <v>-17.69174017497198</v>
+        <v>-18.33483329727525</v>
       </c>
       <c r="F53">
-        <v>1.085713671477512</v>
+        <v>0.8075081359821035</v>
       </c>
       <c r="G53">
-        <v>-7.081075979164743</v>
+        <v>-8.213216342684703</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.01469648943321915</v>
       </c>
       <c r="E54">
-        <v>-17.87575471627366</v>
+        <v>-18.12590762045737</v>
       </c>
       <c r="F54">
-        <v>1.003715239009194</v>
+        <v>0.892551647023112</v>
       </c>
       <c r="G54">
-        <v>-8.019754682460775</v>
+        <v>-8.407158032011827</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.0725532629569203</v>
       </c>
       <c r="E55">
-        <v>-17.38340543673772</v>
+        <v>-17.32126118793046</v>
       </c>
       <c r="F55">
-        <v>1.162369134197772</v>
+        <v>0.9043061804688369</v>
       </c>
       <c r="G55">
-        <v>-8.614772274416142</v>
+        <v>-8.056922177230172</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.1667700809110531</v>
       </c>
       <c r="E56">
-        <v>-17.00403705521914</v>
+        <v>-17.87539243835305</v>
       </c>
       <c r="F56">
-        <v>1.224591123291655</v>
+        <v>0.966528169562719</v>
       </c>
       <c r="G56">
-        <v>-7.777760424631129</v>
+        <v>-8.271700440181469</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.2661619102798615</v>
       </c>
       <c r="E57">
-        <v>-16.15074575490183</v>
+        <v>-16.62101419517638</v>
       </c>
       <c r="F57">
-        <v>0.9000417450792251</v>
+        <v>1.101441054987063</v>
       </c>
       <c r="G57">
-        <v>-7.722355134485886</v>
+        <v>-8.128999374711183</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.3685978013606663</v>
       </c>
       <c r="E58">
-        <v>-15.52750546264818</v>
+        <v>-15.94629421040353</v>
       </c>
       <c r="F58">
-        <v>1.494812853758881</v>
+        <v>0.9303136034471302</v>
       </c>
       <c r="G58">
-        <v>-8.168242581533704</v>
+        <v>-8.434619007260082</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.4711976929957608</v>
       </c>
       <c r="E59">
-        <v>-14.66116762871478</v>
+        <v>-16.66532531334143</v>
       </c>
       <c r="F59">
-        <v>0.580142821466112</v>
+        <v>0.7540436470706178</v>
       </c>
       <c r="G59">
-        <v>-8.243203264179423</v>
+        <v>-8.328568991455068</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5720503404992756</v>
       </c>
       <c r="E60">
-        <v>-15.17180288629369</v>
+        <v>-16.12287752585863</v>
       </c>
       <c r="F60">
-        <v>1.150593063199575</v>
+        <v>0.763876368141848</v>
       </c>
       <c r="G60">
-        <v>-8.196415324072902</v>
+        <v>-8.005042618084254</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.6695131406580948</v>
       </c>
       <c r="E61">
-        <v>-14.97967331957026</v>
+        <v>-15.89829691439623</v>
       </c>
       <c r="F61">
-        <v>1.033120625073771</v>
+        <v>0.6489553016166669</v>
       </c>
       <c r="G61">
-        <v>-8.923914327418824</v>
+        <v>-7.766696581438884</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7613191331645506</v>
       </c>
       <c r="E62">
-        <v>-14.18298794434883</v>
+        <v>-15.85325218344193</v>
       </c>
       <c r="F62">
-        <v>0.7134437039246084</v>
+        <v>0.5880073415882905</v>
       </c>
       <c r="G62">
-        <v>-9.016652639610427</v>
+        <v>-8.406697866181869</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.8458050317523573</v>
       </c>
       <c r="E63">
-        <v>-15.07304139666041</v>
+        <v>-15.26792880405451</v>
       </c>
       <c r="F63">
-        <v>0.357906757908255</v>
+        <v>0.7264059970436151</v>
       </c>
       <c r="G63">
-        <v>-8.723050287369084</v>
+        <v>-8.49549993972728</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.9223930420496816</v>
       </c>
       <c r="E64">
-        <v>-13.92637743623018</v>
+        <v>-15.88306765630844</v>
       </c>
       <c r="F64">
-        <v>0.4908299048310749</v>
+        <v>0.8024965131951665</v>
       </c>
       <c r="G64">
-        <v>-8.698234438006708</v>
+        <v>-8.508798401158531</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.9898938317693362</v>
       </c>
       <c r="E65">
-        <v>-14.19564955767428</v>
+        <v>-16.19508857238494</v>
       </c>
       <c r="F65">
-        <v>0.6230713053813908</v>
+        <v>0.6550081822289229</v>
       </c>
       <c r="G65">
-        <v>-7.771751784477352</v>
+        <v>-8.581733029934215</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.047341051721992</v>
       </c>
       <c r="E66">
-        <v>-13.69415276064284</v>
+        <v>-14.19422761683587</v>
       </c>
       <c r="F66">
-        <v>0.7111822609149658</v>
+        <v>0.8011512445330201</v>
       </c>
       <c r="G66">
-        <v>-7.354851474171392</v>
+        <v>-8.079996679638892</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.095532689852419</v>
       </c>
       <c r="E67">
-        <v>-14.01213767698744</v>
+        <v>-14.99388819948034</v>
       </c>
       <c r="F67">
-        <v>0.409585286699305</v>
+        <v>0.8494400939118145</v>
       </c>
       <c r="G67">
-        <v>-8.918922024745603</v>
+        <v>-8.778253634236432</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.135445991388371</v>
       </c>
       <c r="E68">
-        <v>-14.30502126190753</v>
+        <v>-15.25713292202023</v>
       </c>
       <c r="F68">
-        <v>0.5351757253725437</v>
+        <v>0.6859352792124425</v>
       </c>
       <c r="G68">
-        <v>-8.752881613223456</v>
+        <v>-9.040667336952302</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.167777538898658</v>
       </c>
       <c r="E69">
-        <v>-13.22704066675164</v>
+        <v>-15.54240414213342</v>
       </c>
       <c r="F69">
-        <v>0.7427877908013781</v>
+        <v>0.553328568637492</v>
       </c>
       <c r="G69">
-        <v>-8.368937783760941</v>
+        <v>-8.926175430022147</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.19566782727804</v>
       </c>
       <c r="E70">
-        <v>-12.81859948210382</v>
+        <v>-14.8800378344535</v>
       </c>
       <c r="F70">
-        <v>1.10609150958638</v>
+        <v>0.7445373027560906</v>
       </c>
       <c r="G70">
-        <v>-9.434595771761259</v>
+        <v>-8.753566896150087</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.222377318521061</v>
       </c>
       <c r="E71">
-        <v>-14.50461828226961</v>
+        <v>-14.98847667304117</v>
       </c>
       <c r="F71">
-        <v>1.017066864807517</v>
+        <v>0.4086293507164744</v>
       </c>
       <c r="G71">
-        <v>-8.265443509112245</v>
+        <v>-8.639482186321262</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.249641107609018</v>
       </c>
       <c r="E72">
-        <v>-12.41057944553872</v>
+        <v>-15.81446127509223</v>
       </c>
       <c r="F72">
-        <v>0.6572480876860928</v>
+        <v>0.7163297359559619</v>
       </c>
       <c r="G72">
-        <v>-7.798070621514557</v>
+        <v>-9.130638033073074</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.281473391679884</v>
       </c>
       <c r="E73">
-        <v>-14.95523767382487</v>
+        <v>-15.91332691962769</v>
       </c>
       <c r="F73">
-        <v>0.6256997151504736</v>
+        <v>0.4731765671100147</v>
       </c>
       <c r="G73">
-        <v>-7.450486513709857</v>
+        <v>-8.299303768887912</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.322051583514201</v>
       </c>
       <c r="E74">
-        <v>-14.56985547882411</v>
+        <v>-14.60938452843707</v>
       </c>
       <c r="F74">
-        <v>0.497398858335275</v>
+        <v>0.6831503080042305</v>
       </c>
       <c r="G74">
-        <v>-7.598404998950033</v>
+        <v>-7.538897942881635</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.372189700249507</v>
       </c>
       <c r="E75">
-        <v>-15.70310609924362</v>
+        <v>-16.12940758537769</v>
       </c>
       <c r="F75">
-        <v>0.7054905484903304</v>
+        <v>0.4305802585232585</v>
       </c>
       <c r="G75">
-        <v>-8.84089908747606</v>
+        <v>-8.03271877879256</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.434384404231547</v>
       </c>
       <c r="E76">
-        <v>-15.95049210580864</v>
+        <v>-16.06004947747621</v>
       </c>
       <c r="F76">
-        <v>0.3123084458537534</v>
+        <v>0.4074265612476095</v>
       </c>
       <c r="G76">
-        <v>-7.345826927031339</v>
+        <v>-7.980233389812954</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.511246733467023</v>
       </c>
       <c r="E77">
-        <v>-14.91951707085237</v>
+        <v>-17.17488732258053</v>
       </c>
       <c r="F77">
-        <v>0.5319235549491528</v>
+        <v>0.01643714712624284</v>
       </c>
       <c r="G77">
-        <v>-7.397709796722797</v>
+        <v>-7.345568704479275</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.601562891925871</v>
       </c>
       <c r="E78">
-        <v>-15.41949682909124</v>
+        <v>-16.59643816673675</v>
       </c>
       <c r="F78">
-        <v>0.1370002240318913</v>
+        <v>0.3165844783870045</v>
       </c>
       <c r="G78">
-        <v>-7.383289060353731</v>
+        <v>-7.916846374372529</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.704741718303816</v>
       </c>
       <c r="E79">
-        <v>-15.08858311945473</v>
+        <v>-17.02790211323957</v>
       </c>
       <c r="F79">
-        <v>0.2965827190790076</v>
+        <v>0.1934700298807336</v>
       </c>
       <c r="G79">
-        <v>-7.4254025101588</v>
+        <v>-7.627762916792291</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.821047027923526</v>
       </c>
       <c r="E80">
-        <v>-15.40030062777272</v>
+        <v>-16.75046062468563</v>
       </c>
       <c r="F80">
-        <v>-0.2218046313885062</v>
+        <v>-0.01834020154548881</v>
       </c>
       <c r="G80">
-        <v>-6.515773843969874</v>
+        <v>-7.063063300885569</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.947111329778261</v>
       </c>
       <c r="E81">
-        <v>-15.637800975579</v>
+        <v>-18.22993572536158</v>
       </c>
       <c r="F81">
-        <v>0.2352512249431351</v>
+        <v>0.006033680914483847</v>
       </c>
       <c r="G81">
-        <v>-7.573284579398044</v>
+        <v>-6.850039627070085</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.079121189020445</v>
       </c>
       <c r="E82">
-        <v>-16.74177501153892</v>
+        <v>-18.71120382900075</v>
       </c>
       <c r="F82">
-        <v>0.241725744563416</v>
+        <v>0.3111205669981389</v>
       </c>
       <c r="G82">
-        <v>-6.515651353784921</v>
+        <v>-7.120223180166625</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.214936487718328</v>
       </c>
       <c r="E83">
-        <v>-18.73714745659069</v>
+        <v>-20.00946298531175</v>
       </c>
       <c r="F83">
-        <v>-0.09921619618301294</v>
+        <v>0.03664185644792558</v>
       </c>
       <c r="G83">
-        <v>-4.94612502416199</v>
+        <v>-6.349554662988607</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.350033251377431</v>
       </c>
       <c r="E84">
-        <v>-18.50925200215469</v>
+        <v>-19.78783946737637</v>
       </c>
       <c r="F84">
-        <v>0.1813269921230956</v>
+        <v>-0.1727222060378299</v>
       </c>
       <c r="G84">
-        <v>-5.693411158196136</v>
+        <v>-7.69122276423458</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.478590955123567</v>
       </c>
       <c r="E85">
-        <v>-19.72606655343773</v>
+        <v>-21.17061806256652</v>
       </c>
       <c r="F85">
-        <v>0.05199233278920322</v>
+        <v>-0.06495657713803099</v>
       </c>
       <c r="G85">
-        <v>-6.482741220579026</v>
+        <v>-6.709122945645468</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.597820566170505</v>
       </c>
       <c r="E86">
-        <v>-19.64055085027688</v>
+        <v>-21.53128837490743</v>
       </c>
       <c r="F86">
-        <v>-0.1172066794370126</v>
+        <v>-0.1374702028442941</v>
       </c>
       <c r="G86">
-        <v>-6.731412848761381</v>
+        <v>-6.637674751816918</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.703535623673041</v>
       </c>
       <c r="E87">
-        <v>-22.21808579985873</v>
+        <v>-22.67954635818835</v>
       </c>
       <c r="F87">
-        <v>-0.4256202890103105</v>
+        <v>-0.1117783878464674</v>
       </c>
       <c r="G87">
-        <v>-6.349587768444</v>
+        <v>-6.142715088240482</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.789807367575788</v>
       </c>
       <c r="E88">
-        <v>-21.80642487019146</v>
+        <v>-23.33190473831132</v>
       </c>
       <c r="F88">
-        <v>-0.5347833737186322</v>
+        <v>-0.3934614096988281</v>
       </c>
       <c r="G88">
-        <v>-4.978859698454304</v>
+        <v>-6.139851466349013</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.853698014075337</v>
       </c>
       <c r="E89">
-        <v>-24.46494704892648</v>
+        <v>-25.00971794357521</v>
       </c>
       <c r="F89">
-        <v>-0.1996714827531062</v>
+        <v>-0.7627152915381386</v>
       </c>
       <c r="G89">
-        <v>-5.545403288226399</v>
+        <v>-6.517859487659615</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.892410720973266</v>
       </c>
       <c r="E90">
-        <v>-25.88526669364023</v>
+        <v>-25.48263554114424</v>
       </c>
       <c r="F90">
-        <v>-0.08163492642599623</v>
+        <v>-0.4929234837529647</v>
       </c>
       <c r="G90">
-        <v>-6.757456910518828</v>
+        <v>-6.71115893115212</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.901322578052441</v>
       </c>
       <c r="E91">
-        <v>-27.60459242013243</v>
+        <v>-27.02194084040953</v>
       </c>
       <c r="F91">
-        <v>-0.9549238651119162</v>
+        <v>-0.3443284539365811</v>
       </c>
       <c r="G91">
-        <v>-5.870300227450474</v>
+        <v>-6.275140220356869</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.878838848572308</v>
       </c>
       <c r="E92">
-        <v>-29.49674282865336</v>
+        <v>-29.6172591074195</v>
       </c>
       <c r="F92">
-        <v>-0.6743599676207377</v>
+        <v>-0.6997220923922501</v>
       </c>
       <c r="G92">
-        <v>-5.716187711506322</v>
+        <v>-6.561972506970403</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.826301954266468</v>
       </c>
       <c r="E93">
-        <v>-29.55058185613056</v>
+        <v>-30.57900736022051</v>
       </c>
       <c r="F93">
-        <v>0.02724982683498478</v>
+        <v>-0.8339896796098136</v>
       </c>
       <c r="G93">
-        <v>-6.597948205345663</v>
+        <v>-6.272991676301882</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.743227129013044</v>
       </c>
       <c r="E94">
-        <v>-31.68475655799143</v>
+        <v>-31.63329271513127</v>
       </c>
       <c r="F94">
-        <v>-0.986540163774565</v>
+        <v>-0.8663274862803008</v>
       </c>
       <c r="G94">
-        <v>-6.571559846852132</v>
+        <v>-6.640117934424899</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.632608189954817</v>
       </c>
       <c r="E95">
-        <v>-33.57499142200713</v>
+        <v>-33.31294221660526</v>
       </c>
       <c r="F95">
-        <v>-0.6910606828285785</v>
+        <v>-0.9936889744607247</v>
       </c>
       <c r="G95">
-        <v>-5.998299160180856</v>
+        <v>-6.514466178481862</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.501935474041127</v>
       </c>
       <c r="E96">
-        <v>-35.24239819400139</v>
+        <v>-35.94450186109862</v>
       </c>
       <c r="F96">
-        <v>-0.8503590478565346</v>
+        <v>-0.9255259343539646</v>
       </c>
       <c r="G96">
-        <v>-5.737494382597071</v>
+        <v>-6.70789142270486</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.357803697086783</v>
       </c>
       <c r="E97">
-        <v>-36.01630987343825</v>
+        <v>-37.99881692383423</v>
       </c>
       <c r="F97">
-        <v>-2.031002114207572</v>
+        <v>-1.237819616841976</v>
       </c>
       <c r="G97">
-        <v>-6.317396023620127</v>
+        <v>-6.171609529707241</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.208206177883584</v>
       </c>
       <c r="E98">
-        <v>-38.80739860027381</v>
+        <v>-39.72525914722949</v>
       </c>
       <c r="F98">
-        <v>-0.9851915816428074</v>
+        <v>-1.653766084074886</v>
       </c>
       <c r="G98">
-        <v>-6.325182426728492</v>
+        <v>-6.763362923760887</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.066274807458762</v>
       </c>
       <c r="E99">
-        <v>-41.37811819647411</v>
+        <v>-41.06291829164422</v>
       </c>
       <c r="F99">
-        <v>-1.915692543370478</v>
+        <v>-1.773554637458916</v>
       </c>
       <c r="G99">
-        <v>-6.782044332238994</v>
+        <v>-7.002142641871901</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.94078839478618</v>
       </c>
       <c r="E100">
-        <v>-42.88183648275012</v>
+        <v>-44.31086664721762</v>
       </c>
       <c r="F100">
-        <v>-1.876472660317533</v>
+        <v>-2.167361329117204</v>
       </c>
       <c r="G100">
-        <v>-6.399070492619486</v>
+        <v>-6.702733592754675</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.840382452813737</v>
       </c>
       <c r="E101">
-        <v>-45.45336214732379</v>
+        <v>-45.79775033137011</v>
       </c>
       <c r="F101">
-        <v>-1.993374353302807</v>
+        <v>-2.059477243678805</v>
       </c>
       <c r="G101">
-        <v>-5.904663690148109</v>
+        <v>-7.143731364040989</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.770477921281488</v>
       </c>
       <c r="E102">
-        <v>-48.11676149256507</v>
+        <v>-47.84942076528525</v>
       </c>
       <c r="F102">
-        <v>-2.061162971343502</v>
+        <v>-2.458458746502381</v>
       </c>
       <c r="G102">
-        <v>-6.20400321780901</v>
+        <v>-6.548270158983359</v>
       </c>
     </row>
   </sheetData>
